--- a/dataset_t6_grouped/results2/G5/G5_T12594_W0065F0001T0006Z000C1N26_analysis.xlsx
+++ b/dataset_t6_grouped/results2/G5/G5_T12594_W0065F0001T0006Z000C1N26_analysis.xlsx
@@ -480,16 +480,16 @@
         <v>1</v>
       </c>
       <c r="C2" t="n">
-        <v>38.69338108010013</v>
+        <v>6.287674425516272</v>
       </c>
       <c r="D2" t="n">
-        <v>39.4944599063123</v>
+        <v>6.417849734775749</v>
       </c>
       <c r="E2" t="n">
-        <v>10.54007313264421</v>
+        <v>1.712761884054685</v>
       </c>
       <c r="F2" t="n">
-        <v>11.22947607878172</v>
+        <v>1.82478986280203</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -512,16 +512,16 @@
         <v>2</v>
       </c>
       <c r="C3" t="n">
-        <v>23.77457154763761</v>
+        <v>3.863367876491112</v>
       </c>
       <c r="D3" t="n">
-        <v>24.56572665108137</v>
+        <v>3.991930580800723</v>
       </c>
       <c r="E3" t="n">
-        <v>10.54007313264421</v>
+        <v>1.712761884054685</v>
       </c>
       <c r="F3" t="n">
-        <v>11.22947607878172</v>
+        <v>1.82478986280203</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -544,16 +544,16 @@
         <v>3</v>
       </c>
       <c r="C4" t="n">
-        <v>31.05276223403095</v>
+        <v>5.046073863030029</v>
       </c>
       <c r="D4" t="n">
-        <v>31.69191328185996</v>
+        <v>5.149935908302243</v>
       </c>
       <c r="E4" t="n">
-        <v>10.54007313264421</v>
+        <v>1.712761884054685</v>
       </c>
       <c r="F4" t="n">
-        <v>11.22947607878172</v>
+        <v>1.82478986280203</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
@@ -576,16 +576,16 @@
         <v>4</v>
       </c>
       <c r="C5" t="n">
-        <v>39.02088113452158</v>
+        <v>6.340893184359757</v>
       </c>
       <c r="D5" t="n">
-        <v>39.11534087928732</v>
+        <v>6.356242892884191</v>
       </c>
       <c r="E5" t="n">
-        <v>10.54007313264421</v>
+        <v>1.712761884054685</v>
       </c>
       <c r="F5" t="n">
-        <v>11.22947607878172</v>
+        <v>1.82478986280203</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
@@ -608,16 +608,16 @@
         <v>5</v>
       </c>
       <c r="C6" t="n">
-        <v>41.93979747592577</v>
+        <v>6.815217089837939</v>
       </c>
       <c r="D6" t="n">
-        <v>32.75194650703985</v>
+        <v>5.322191307393975</v>
       </c>
       <c r="E6" t="n">
-        <v>10.54007313264421</v>
+        <v>1.712761884054685</v>
       </c>
       <c r="F6" t="n">
-        <v>11.22947607878172</v>
+        <v>1.82478986280203</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
@@ -640,16 +640,16 @@
         <v>6</v>
       </c>
       <c r="C7" t="n">
-        <v>26.17378015088111</v>
+        <v>4.25323927451818</v>
       </c>
       <c r="D7" t="n">
-        <v>11.78921762775271</v>
+        <v>1.915747864509815</v>
       </c>
       <c r="E7" t="n">
-        <v>10.54007313264421</v>
+        <v>1.712761884054685</v>
       </c>
       <c r="F7" t="n">
-        <v>11.22947607878172</v>
+        <v>1.82478986280203</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
@@ -672,16 +672,16 @@
         <v>7</v>
       </c>
       <c r="C8" t="n">
-        <v>43.89622669646424</v>
+        <v>7.133136838175439</v>
       </c>
       <c r="D8" t="n">
-        <v>16.79042044921996</v>
+        <v>2.728443322998243</v>
       </c>
       <c r="E8" t="n">
-        <v>10.54007313264421</v>
+        <v>1.712761884054685</v>
       </c>
       <c r="F8" t="n">
-        <v>11.22947607878172</v>
+        <v>1.82478986280203</v>
       </c>
       <c r="G8" t="inlineStr">
         <is>
@@ -704,16 +704,16 @@
         <v>8</v>
       </c>
       <c r="C9" t="n">
-        <v>10.74220540044976</v>
+        <v>1.745608377573086</v>
       </c>
       <c r="D9" t="n">
-        <v>9.003885041236593</v>
+        <v>1.463131319200947</v>
       </c>
       <c r="E9" t="n">
-        <v>10.54007313264421</v>
+        <v>1.712761884054685</v>
       </c>
       <c r="F9" t="n">
-        <v>11.22947607878172</v>
+        <v>1.82478986280203</v>
       </c>
       <c r="G9" t="inlineStr">
         <is>
